--- a/AAII_Financials/Yearly/MTSI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTSI_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/MTSI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTSI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>MTSI</t>
   </si>
@@ -656,211 +656,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E7" s="2">
         <v>45198</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44470</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44106</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43735</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43371</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43007</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42643</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42279</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41915</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41544</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41180</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40816</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>729600</v>
+      </c>
+      <c r="E8" s="3">
         <v>648400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>675200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>606900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>530000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>499700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>570400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>698800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>544300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>420600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>339200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>242700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>303300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>310300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>335800</v>
+      </c>
+      <c r="E9" s="3">
         <v>262600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>269000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>265100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>259900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>279000</v>
       </c>
-      <c r="I9" s="3">
-        <v>324700</v>
-      </c>
       <c r="J9" s="3">
+        <v>307500</v>
+      </c>
+      <c r="K9" s="3">
         <v>371900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>262700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>217000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>196800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>133500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>336500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>178400</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>393800</v>
+      </c>
+      <c r="E10" s="3">
         <v>385800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>406200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>341900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>270200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>220700</v>
       </c>
-      <c r="I10" s="3">
-        <v>245700</v>
-      </c>
       <c r="J10" s="3">
+        <v>262900</v>
+      </c>
+      <c r="K10" s="3">
         <v>326900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>281600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>203600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>142300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>109200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-33200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>131900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,53 +890,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>182200</v>
+      </c>
+      <c r="E12" s="3">
         <v>148500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>148200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>138800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>141300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>163500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>177700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>148000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>107700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>82200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>66900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>42500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>72600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>36100</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -967,99 +983,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>35</v>
+      <c r="D14" s="3">
+        <v>7700</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="F14" s="3">
-        <v>4400</v>
+        <v>-118200</v>
       </c>
       <c r="G14" s="3">
-        <v>1100</v>
+        <v>-5400</v>
       </c>
       <c r="H14" s="3">
-        <v>284500</v>
+        <v>3400</v>
       </c>
       <c r="I14" s="3">
-        <v>16300</v>
+        <v>284300</v>
       </c>
       <c r="J14" s="3">
+        <v>64400</v>
+      </c>
+      <c r="K14" s="3">
         <v>9400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>17400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>36200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1700</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>23700</v>
+        <v>67200</v>
       </c>
       <c r="E15" s="3">
-        <v>25600</v>
+        <v>52200</v>
       </c>
       <c r="F15" s="3">
-        <v>30900</v>
+        <v>57200</v>
       </c>
       <c r="G15" s="3">
-        <v>32900</v>
+        <v>70000</v>
       </c>
       <c r="H15" s="3">
-        <v>44900</v>
+        <v>78800</v>
       </c>
       <c r="I15" s="3">
-        <v>48300</v>
+        <v>104400</v>
       </c>
       <c r="J15" s="3">
+        <v>112400</v>
+      </c>
+      <c r="K15" s="3">
         <v>35500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>23600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>11700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1800</v>
-      </c>
-      <c r="N15" s="3">
-        <v>1300</v>
       </c>
       <c r="O15" s="3">
         <v>1300</v>
       </c>
       <c r="P15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q15" s="3">
         <v>1100</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1074,98 +1099,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>541000</v>
+        <v>648200</v>
       </c>
       <c r="E17" s="3">
+        <v>531900</v>
+      </c>
+      <c r="F17" s="3">
         <v>542500</v>
       </c>
-      <c r="F17" s="3">
-        <v>530300</v>
-      </c>
       <c r="G17" s="3">
-        <v>526600</v>
+        <v>525900</v>
       </c>
       <c r="H17" s="3">
-        <v>880100</v>
+        <v>525500</v>
       </c>
       <c r="I17" s="3">
-        <v>676900</v>
+        <v>595800</v>
       </c>
       <c r="J17" s="3">
+        <v>646900</v>
+      </c>
+      <c r="K17" s="3">
         <v>714900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>531100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>410500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>367000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>235000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>249600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>264400</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>107400</v>
+        <v>81400</v>
       </c>
       <c r="E18" s="3">
+        <v>116500</v>
+      </c>
+      <c r="F18" s="3">
         <v>132700</v>
       </c>
-      <c r="F18" s="3">
-        <v>76600</v>
-      </c>
       <c r="G18" s="3">
-        <v>3400</v>
+        <v>81000</v>
       </c>
       <c r="H18" s="3">
-        <v>-380400</v>
+        <v>4500</v>
       </c>
       <c r="I18" s="3">
-        <v>-106500</v>
+        <v>-96000</v>
       </c>
       <c r="J18" s="3">
+        <v>-76500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-16100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>13200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-27800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>53700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>45900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1183,233 +1215,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>20100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>114700</v>
+        <v>700</v>
       </c>
       <c r="F20" s="3">
-        <v>-13100</v>
+        <v>3500</v>
       </c>
       <c r="G20" s="3">
-        <v>-17600</v>
+        <v>22900</v>
       </c>
       <c r="H20" s="3">
-        <v>-7000</v>
+        <v>15300</v>
       </c>
       <c r="I20" s="3">
-        <v>-17400</v>
+        <v>7000</v>
       </c>
       <c r="J20" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-4600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-16400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-40800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-44800</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>179700</v>
+        <v>148600</v>
       </c>
       <c r="E21" s="3">
-        <v>304600</v>
+        <v>168000</v>
       </c>
       <c r="F21" s="3">
-        <v>133500</v>
+        <v>186400</v>
       </c>
       <c r="G21" s="3">
-        <v>64600</v>
+        <v>128100</v>
       </c>
       <c r="H21" s="3">
-        <v>-282900</v>
+        <v>68100</v>
       </c>
       <c r="I21" s="3">
-        <v>-11500</v>
+        <v>1400</v>
       </c>
       <c r="J21" s="3">
+        <v>52900</v>
+      </c>
+      <c r="K21" s="3">
         <v>72300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>67400</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>24100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>25600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E22" s="3">
         <v>12400</v>
       </c>
-      <c r="E22" s="3">
-        <v>4300</v>
-      </c>
       <c r="F22" s="3">
-        <v>20600</v>
+        <v>8600</v>
       </c>
       <c r="G22" s="3">
+        <v>22100</v>
+      </c>
+      <c r="H22" s="3">
         <v>27400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>35800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>31300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>18400</v>
       </c>
       <c r="L22" s="3">
         <v>18400</v>
       </c>
       <c r="M22" s="3">
+        <v>18400</v>
+      </c>
+      <c r="N22" s="3">
         <v>12400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1600</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>91500</v>
+      </c>
+      <c r="E23" s="3">
         <v>115200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>243100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>42900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-41600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-423200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-155200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-21600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-15400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-40900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E24" s="3">
         <v>23600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-196800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-39400</v>
       </c>
-      <c r="I24" s="3">
-        <v>-24100</v>
-      </c>
       <c r="J24" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="K24" s="3">
         <v>100900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-18000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-9900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-16100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>16000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1452,99 +1500,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E26" s="3">
         <v>91600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>440000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>38000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-46100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-383800</v>
       </c>
-      <c r="I26" s="3">
-        <v>-131200</v>
-      </c>
       <c r="J26" s="3">
+        <v>-133800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-150400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E27" s="3">
         <v>91600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>440000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>38000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-46100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-383800</v>
       </c>
-      <c r="I27" s="3">
-        <v>-158800</v>
-      </c>
       <c r="J27" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="K27" s="3">
         <v>-150400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-82200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1587,20 +1644,23 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>35</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1609,32 +1669,35 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-8800</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="K29" s="3">
         <v>-19100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>5000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>54100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>9500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>15500</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>800</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1677,9 +1740,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1722,99 +1788,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-20100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-114700</v>
+        <v>-700</v>
       </c>
       <c r="F32" s="3">
-        <v>13100</v>
+        <v>-3500</v>
       </c>
       <c r="G32" s="3">
-        <v>17600</v>
+        <v>-22900</v>
       </c>
       <c r="H32" s="3">
-        <v>7000</v>
+        <v>-15300</v>
       </c>
       <c r="I32" s="3">
-        <v>17400</v>
+        <v>-7000</v>
       </c>
       <c r="J32" s="3">
+        <v>17000</v>
+      </c>
+      <c r="K32" s="3">
         <v>4600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>16400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>40800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>44800</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E33" s="3">
         <v>91600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>440000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>38000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-46100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-383800</v>
       </c>
-      <c r="I33" s="3">
-        <v>-167600</v>
-      </c>
       <c r="J33" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="K33" s="3">
         <v>-169500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>48600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-81500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1857,104 +1932,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E35" s="3">
         <v>91600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>440000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>38000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-46100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-383800</v>
       </c>
-      <c r="I35" s="3">
-        <v>-167600</v>
-      </c>
       <c r="J35" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="K35" s="3">
         <v>-169500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>48600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-81500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E38" s="2">
         <v>45198</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44470</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44106</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43735</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43371</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43007</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42643</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42279</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41915</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41544</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41180</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40816</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1972,8 +2056,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1991,85 +2076,89 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>146800</v>
+      </c>
+      <c r="E41" s="3">
         <v>174000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>120000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>156500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>129400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>75500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>130100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>333000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>122300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>173900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>110500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>435100</v>
+      </c>
+      <c r="E42" s="3">
         <v>340600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>466600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>188400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>203700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>101200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>98200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>84100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>23800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>39600</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>35</v>
@@ -2080,212 +2169,227 @@
       <c r="P42" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>105700</v>
+      </c>
+      <c r="E43" s="3">
         <v>91300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>101600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>84600</v>
       </c>
-      <c r="G43" s="3">
-        <v>47100</v>
-      </c>
       <c r="H43" s="3">
+        <v>45900</v>
+      </c>
+      <c r="I43" s="3">
         <v>86500</v>
       </c>
-      <c r="I43" s="3">
-        <v>115000</v>
-      </c>
       <c r="J43" s="3">
+        <v>122400</v>
+      </c>
+      <c r="K43" s="3">
         <v>154600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>129900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>99800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>75200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>128000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>59100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46200</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>194500</v>
+      </c>
+      <c r="E44" s="3">
         <v>136300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>115000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>82700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>91600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>107900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>122800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>136100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>114900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>79900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>73600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>54900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>57500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>52500</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>19100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>10000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>9400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>9700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>27500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>28200</v>
+      <c r="D45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="J45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="K45" s="3">
         <v>58000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>50700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12200</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>903100</v>
+      </c>
+      <c r="E46" s="3">
         <v>761200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>813100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>521500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>481500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>398600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>458900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>562900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>612900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>384200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>373300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>246400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>213000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>156500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>2500</v>
-      </c>
-      <c r="E47" s="3">
-        <v>2500</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" s="3">
         <v>15300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>17700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>23600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>31100</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>35</v>
@@ -2302,102 +2406,111 @@
       <c r="O47" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E48" s="3">
         <v>175100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>149200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>150500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>152200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>132600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>149900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>131000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>99200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>83800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>25400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>408300</v>
+      </c>
+      <c r="E49" s="3">
         <v>390400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>362700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>398900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>445900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>496000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>826900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>934900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>379600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>337000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>153400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>21000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>22800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>26100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2440,9 +2553,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2485,54 +2601,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>224100</v>
+        <v>26500</v>
       </c>
       <c r="E52" s="3">
-        <v>244300</v>
+        <v>8500</v>
       </c>
       <c r="F52" s="3">
-        <v>47900</v>
+        <v>9400</v>
       </c>
       <c r="G52" s="3">
-        <v>49100</v>
+        <v>8400</v>
       </c>
       <c r="H52" s="3">
-        <v>54800</v>
+        <v>7100</v>
       </c>
       <c r="I52" s="3">
-        <v>15800</v>
+        <v>11000</v>
       </c>
       <c r="J52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="K52" s="3">
         <v>8300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>96800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>55800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>105100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3300</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2575,54 +2697,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1755600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1553200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1571800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1134100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1146400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1105600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1482500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1637100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1188600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>860800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>682200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>316600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>268100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>211300</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2640,8 +2768,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2659,278 +2788,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E57" s="3">
         <v>25000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>23000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>42000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>47000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>26000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1200</v>
+        <v>8400</v>
       </c>
       <c r="E58" s="3">
-        <v>1000</v>
+        <v>8400</v>
       </c>
       <c r="F58" s="3">
-        <v>1000</v>
+        <v>7500</v>
       </c>
       <c r="G58" s="3">
-        <v>8300</v>
+        <v>8400</v>
       </c>
       <c r="H58" s="3">
+        <v>15900</v>
+      </c>
+      <c r="I58" s="3">
         <v>8000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3500</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>57400</v>
+        <v>6000</v>
       </c>
       <c r="E59" s="3">
-        <v>65500</v>
+        <v>3800</v>
       </c>
       <c r="F59" s="3">
-        <v>63400</v>
+        <v>5800</v>
       </c>
       <c r="G59" s="3">
-        <v>63700</v>
+        <v>4100</v>
       </c>
       <c r="H59" s="3">
-        <v>42000</v>
+        <v>8200</v>
       </c>
       <c r="I59" s="3">
-        <v>57700</v>
+        <v>9200</v>
       </c>
       <c r="J59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K59" s="3">
         <v>62400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>108700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>52400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>44700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>28800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>46600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E60" s="3">
         <v>83500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>97200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>95000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>74800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>107000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>117100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>92200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>71500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>85600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>52200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>55700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>67100</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>488200</v>
+        <v>512600</v>
       </c>
       <c r="E61" s="3">
-        <v>602500</v>
+        <v>511000</v>
       </c>
       <c r="F61" s="3">
-        <v>528900</v>
+        <v>626600</v>
       </c>
       <c r="G61" s="3">
-        <v>681200</v>
+        <v>557500</v>
       </c>
       <c r="H61" s="3">
+        <v>713000</v>
+      </c>
+      <c r="I61" s="3">
         <v>684800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>687400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>678700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>576300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>335100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>343200</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>33900</v>
+        <v>8500</v>
       </c>
       <c r="E62" s="3">
-        <v>29400</v>
+        <v>11100</v>
       </c>
       <c r="F62" s="3">
-        <v>40500</v>
+        <v>5200</v>
       </c>
       <c r="G62" s="3">
-        <v>70200</v>
+        <v>8800</v>
       </c>
       <c r="H62" s="3">
-        <v>32100</v>
+        <v>32700</v>
       </c>
       <c r="I62" s="3">
-        <v>19400</v>
+        <v>23500</v>
       </c>
       <c r="J62" s="3">
+        <v>19000</v>
+      </c>
+      <c r="K62" s="3">
         <v>63900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>57300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>24800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>17300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>107000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2973,9 +3121,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3018,9 +3169,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3063,54 +3217,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>629300</v>
+      </c>
+      <c r="E66" s="3">
         <v>605600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>729100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>662400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>846300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>791700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>813800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>859700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>725800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>436300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>453700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>69500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>68600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>174100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3128,8 +3288,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3172,9 +3333,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3217,9 +3381,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3260,11 +3427,14 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>182000</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3307,54 +3477,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-185900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-262700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-354300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-801800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-839700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-791800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-408000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-267000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-97500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-98900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-147500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-132200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-147700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-144700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3397,9 +3573,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3442,9 +3621,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3487,54 +3669,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1126300</v>
+      </c>
+      <c r="E76" s="3">
         <v>947600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>842700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>471700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>300100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>313900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>668700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>777400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>462800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>424500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>228600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>247100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>199500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-144800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3577,104 +3765,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45562</v>
+      </c>
+      <c r="E80" s="2">
         <v>45198</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44470</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44106</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43735</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43371</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43007</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42643</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42279</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41915</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41544</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41180</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40816</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E81" s="3">
         <v>91600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>440000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>38000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-46100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-383800</v>
       </c>
-      <c r="I81" s="3">
-        <v>-167600</v>
-      </c>
       <c r="J81" s="3">
+        <v>-140000</v>
+      </c>
+      <c r="K81" s="3">
         <v>-169500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>48600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-81500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3692,53 +3889,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>52200</v>
+        <v>30100</v>
       </c>
       <c r="E83" s="3">
-        <v>57200</v>
+        <v>24000</v>
       </c>
       <c r="F83" s="3">
-        <v>70000</v>
+        <v>23800</v>
       </c>
       <c r="G83" s="3">
-        <v>78800</v>
+        <v>23700</v>
       </c>
       <c r="H83" s="3">
-        <v>104400</v>
+        <v>28500</v>
       </c>
       <c r="I83" s="3">
-        <v>112400</v>
+        <v>29700</v>
       </c>
       <c r="J83" s="3">
+        <v>30700</v>
+      </c>
+      <c r="K83" s="3">
         <v>93000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>70600</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>52700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10400</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3781,9 +3982,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3826,9 +4030,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3871,9 +4078,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3916,9 +4126,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3961,54 +4174,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>162600</v>
+      </c>
+      <c r="E89" s="3">
         <v>166900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>177000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>148400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>171400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>36300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>61100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>79200</v>
-      </c>
-      <c r="L89" s="3">
-        <v>25300</v>
       </c>
       <c r="M89" s="3">
         <v>25300</v>
       </c>
       <c r="N89" s="3">
+        <v>25300</v>
+      </c>
+      <c r="O89" s="3">
         <v>28900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>32800</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4026,53 +4245,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-24700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-26500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-18000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-53000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-31300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-17000</v>
       </c>
       <c r="M91" s="3">
         <v>-17000</v>
       </c>
       <c r="N91" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-12300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4115,9 +4338,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4160,54 +4386,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-181100</v>
+      </c>
+      <c r="E94" s="3">
         <v>36300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-182900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-107200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-33900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-67100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-337600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-94900</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="M94" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-264200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4225,8 +4457,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4264,14 +4497,17 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-79100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4314,9 +4550,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4359,9 +4598,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4404,83 +4646,89 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-149000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-28900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-119100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>73700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>227400</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="M100" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>302400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>10200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>24200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="F101" s="3">
-        <v>400</v>
       </c>
       <c r="G101" s="3">
         <v>400</v>
       </c>
       <c r="H101" s="3">
+        <v>400</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-1100</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>35</v>
@@ -4494,52 +4742,58 @@
       <c r="P101" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E102" s="3">
         <v>54000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-36600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>27100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>53900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-35400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-202900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>210700</v>
-      </c>
-      <c r="L102" s="3">
-        <v>63400</v>
       </c>
       <c r="M102" s="3">
         <v>63400</v>
       </c>
       <c r="N102" s="3">
+        <v>63400</v>
+      </c>
+      <c r="O102" s="3">
         <v>25900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>38900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>21700</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
